--- a/apps/step-up/public/templates/student-import-template.xlsx
+++ b/apps/step-up/public/templates/student-import-template.xlsx
@@ -19,7 +19,7 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Age Range</t>
+    <t>Age</t>
   </si>
   <si>
     <t>Ada Lovelace</t>
@@ -31,7 +31,7 @@
     <t>Female</t>
   </si>
   <si>
-    <t>20-40</t>
+    <t>28</t>
   </si>
   <si>
     <t>Alan Turing</t>
@@ -43,7 +43,7 @@
     <t>Male</t>
   </si>
   <si>
-    <t>10-20</t>
+    <t>16</t>
   </si>
 </sst>
 </file>
